--- a/backend/templates/DVwithBUR.xlsx
+++ b/backend/templates/DVwithBUR.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15210" windowHeight="7620"/>
+    <workbookView windowWidth="19635" windowHeight="7620"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="98">
   <si>
     <t>Fund Cluster:</t>
   </si>
@@ -189,9 +189,6 @@
   </si>
   <si>
     <t>Check/ ADA No. :</t>
-  </si>
-  <si>
-    <t>O</t>
   </si>
   <si>
     <t>Date :</t>
@@ -4642,7 +4639,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="39721155"/>
+          <a:off x="9525" y="39740205"/>
           <a:ext cx="12099925" cy="7910195"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4673,7 +4670,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="95885" y="46093380"/>
+          <a:off x="95885" y="46112430"/>
           <a:ext cx="5667375" cy="1224915"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4792,7 +4789,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10504170" y="46410880"/>
+          <a:off x="10504170" y="46429930"/>
           <a:ext cx="1276350" cy="695325"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5080,7 +5077,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9385300" y="46269275"/>
+          <a:off x="9385300" y="46288325"/>
           <a:ext cx="953770" cy="906145"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -5122,7 +5119,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="64770" y="47316390"/>
+          <a:off x="64770" y="47335440"/>
           <a:ext cx="2668270" cy="297815"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6961,9 +6958,7 @@
         <v>53</v>
       </c>
       <c r="B58" s="28"/>
-      <c r="C58" s="80" t="s">
-        <v>54</v>
-      </c>
+      <c r="C58" s="80"/>
       <c r="D58" s="28"/>
       <c r="E58" s="28"/>
       <c r="F58" s="28"/>
@@ -6971,17 +6966,17 @@
       <c r="H58" s="28"/>
       <c r="I58" s="136"/>
       <c r="J58" s="155" t="s">
+        <v>54</v>
+      </c>
+      <c r="K58" s="156" t="s">
         <v>55</v>
-      </c>
-      <c r="K58" s="156" t="s">
-        <v>56</v>
       </c>
       <c r="L58" s="28"/>
       <c r="M58" s="28"/>
       <c r="N58" s="28"/>
       <c r="O58" s="136"/>
       <c r="P58" s="157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q58" s="88"/>
     </row>
@@ -7006,7 +7001,7 @@
     </row>
     <row r="60" ht="15.75" spans="1:17">
       <c r="A60" s="79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B60" s="28"/>
       <c r="C60" s="80"/>
@@ -7017,10 +7012,10 @@
       <c r="H60" s="28"/>
       <c r="I60" s="136"/>
       <c r="J60" s="155" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K60" s="156" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L60" s="28"/>
       <c r="M60" s="28"/>
@@ -7048,13 +7043,13 @@
       <c r="N61" s="26"/>
       <c r="O61" s="148"/>
       <c r="P61" s="157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q61" s="88"/>
     </row>
     <row r="62" ht="16.5" spans="1:17">
       <c r="A62" s="81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B62" s="82"/>
       <c r="C62" s="82"/>
@@ -7556,7 +7551,7 @@
       </c>
       <c r="B90" s="2"/>
       <c r="C90" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" s="2"/>
@@ -7602,7 +7597,7 @@
       </c>
       <c r="B92" s="28"/>
       <c r="C92" s="29" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D92" s="28"/>
       <c r="E92" s="28"/>
@@ -7694,7 +7689,7 @@
       <c r="I96" s="36"/>
       <c r="J96" s="106"/>
       <c r="K96" s="193" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L96" s="194"/>
       <c r="M96" s="16"/>
@@ -8536,9 +8531,7 @@
         <v>53</v>
       </c>
       <c r="B136" s="28"/>
-      <c r="C136" s="80" t="s">
-        <v>54</v>
-      </c>
+      <c r="C136" s="80"/>
       <c r="D136" s="28"/>
       <c r="E136" s="28"/>
       <c r="F136" s="28"/>
@@ -8546,17 +8539,17 @@
       <c r="H136" s="28"/>
       <c r="I136" s="136"/>
       <c r="J136" s="155" t="s">
+        <v>54</v>
+      </c>
+      <c r="K136" s="156" t="s">
         <v>55</v>
-      </c>
-      <c r="K136" s="156" t="s">
-        <v>56</v>
       </c>
       <c r="L136" s="28"/>
       <c r="M136" s="28"/>
       <c r="N136" s="28"/>
       <c r="O136" s="136"/>
       <c r="P136" s="157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q136" s="88"/>
     </row>
@@ -8581,7 +8574,7 @@
     </row>
     <row r="138" ht="15.75" spans="1:17">
       <c r="A138" s="79" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B138" s="28"/>
       <c r="C138" s="80"/>
@@ -8592,10 +8585,10 @@
       <c r="H138" s="28"/>
       <c r="I138" s="136"/>
       <c r="J138" s="155" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K138" s="156" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L138" s="28"/>
       <c r="M138" s="28"/>
@@ -8623,13 +8616,13 @@
       <c r="N139" s="26"/>
       <c r="O139" s="148"/>
       <c r="P139" s="157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q139" s="88"/>
     </row>
     <row r="140" ht="16.5" spans="1:17">
       <c r="A140" s="81" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B140" s="82"/>
       <c r="C140" s="82"/>
@@ -8977,7 +8970,7 @@
       <c r="B163" s="199"/>
       <c r="C163" s="199"/>
       <c r="D163" s="200" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E163" s="201"/>
       <c r="F163" s="201"/>
@@ -9035,7 +9028,7 @@
     </row>
     <row r="166" spans="1:17">
       <c r="A166" s="210" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B166" s="211"/>
       <c r="C166" s="211"/>
@@ -9094,7 +9087,7 @@
       <c r="P168" s="213"/>
       <c r="Q168" s="249"/>
     </row>
-    <row r="169" spans="1:17">
+    <row r="169" ht="15.75" spans="1:17">
       <c r="A169" s="214"/>
       <c r="B169" s="215"/>
       <c r="C169" s="215"/>
@@ -9113,9 +9106,9 @@
       <c r="P169" s="217"/>
       <c r="Q169" s="252"/>
     </row>
-    <row r="170" spans="1:17">
+    <row r="170" ht="15.75" spans="1:17">
       <c r="A170" s="210" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B170" s="211"/>
       <c r="C170" s="211"/>
@@ -9134,7 +9127,7 @@
       </c>
       <c r="M170" s="211"/>
       <c r="N170" s="218" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="O170" s="211"/>
       <c r="P170" s="218" t="s">
@@ -9457,7 +9450,7 @@
       <c r="H187" s="199"/>
       <c r="I187" s="199"/>
       <c r="J187" s="241" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K187" s="242"/>
       <c r="L187" s="225"/>
@@ -9498,7 +9491,7 @@
       </c>
       <c r="D189" s="228"/>
       <c r="E189" s="229" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F189" s="228"/>
       <c r="G189" s="228"/>
@@ -9513,7 +9506,7 @@
       </c>
       <c r="O189" s="228"/>
       <c r="P189" s="230" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q189" s="247"/>
     </row>
@@ -9522,7 +9515,7 @@
       <c r="B190" s="189"/>
       <c r="C190" s="189"/>
       <c r="D190" s="229" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E190" s="228"/>
       <c r="F190" s="228"/>
@@ -9534,7 +9527,7 @@
       <c r="L190" s="197"/>
       <c r="M190" s="189"/>
       <c r="N190" s="230" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O190" s="231"/>
       <c r="P190" s="231"/>
@@ -9545,7 +9538,7 @@
       <c r="B191" s="189"/>
       <c r="C191" s="189"/>
       <c r="D191" s="230" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E191" s="231"/>
       <c r="F191" s="231"/>
@@ -9557,7 +9550,7 @@
       <c r="L191" s="197"/>
       <c r="M191" s="189"/>
       <c r="N191" s="230" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O191" s="231"/>
       <c r="P191" s="231"/>
@@ -9622,7 +9615,7 @@
     </row>
     <row r="195" ht="18" spans="1:17">
       <c r="A195" s="257" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B195" s="230"/>
       <c r="C195" s="189"/>
@@ -9635,7 +9628,7 @@
       <c r="J195" s="189"/>
       <c r="K195" s="234"/>
       <c r="L195" s="257" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M195" s="230"/>
       <c r="N195" s="189"/>
@@ -9645,13 +9638,13 @@
     </row>
     <row r="196" ht="18" spans="1:17">
       <c r="A196" s="257" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B196" s="230"/>
       <c r="C196" s="189"/>
       <c r="D196" s="189"/>
       <c r="E196" s="258" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F196" s="259"/>
       <c r="G196" s="259"/>
@@ -9660,25 +9653,25 @@
       <c r="J196" s="259"/>
       <c r="K196" s="285"/>
       <c r="L196" s="257" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M196" s="230"/>
       <c r="N196" s="189"/>
       <c r="O196" s="258" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P196" s="259"/>
       <c r="Q196" s="285"/>
     </row>
     <row r="197" ht="18" spans="1:17">
       <c r="A197" s="257" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B197" s="230"/>
       <c r="C197" s="189"/>
       <c r="D197" s="189"/>
       <c r="E197" s="229" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F197" s="229"/>
       <c r="G197" s="229"/>
@@ -9687,19 +9680,19 @@
       <c r="J197" s="229"/>
       <c r="K197" s="229"/>
       <c r="L197" s="257" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M197" s="230"/>
       <c r="N197" s="189"/>
       <c r="O197" s="229" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P197" s="229"/>
       <c r="Q197" s="300"/>
     </row>
     <row r="198" ht="18" spans="1:17">
       <c r="A198" s="257" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B198" s="231"/>
       <c r="C198" s="189"/>
@@ -9712,16 +9705,16 @@
       <c r="J198" s="189"/>
       <c r="K198" s="234"/>
       <c r="L198" s="257" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M198" s="231"/>
       <c r="N198" s="189"/>
       <c r="O198" s="286"/>
       <c r="P198" s="222" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q198" s="301" t="s">
         <v>83</v>
-      </c>
-      <c r="Q198" s="301" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="199" ht="15.75" spans="1:17">
@@ -9750,7 +9743,7 @@
       <c r="B200" s="261"/>
       <c r="C200" s="262"/>
       <c r="D200" s="263" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E200" s="264"/>
       <c r="F200" s="264"/>
@@ -9768,7 +9761,7 @@
     </row>
     <row r="201" ht="18.75" spans="1:17">
       <c r="A201" s="265" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B201" s="264"/>
       <c r="C201" s="264"/>
@@ -9801,24 +9794,24 @@
       <c r="E202" s="203"/>
       <c r="F202" s="244"/>
       <c r="G202" s="268" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H202" s="269"/>
       <c r="I202" s="289"/>
       <c r="J202" s="267" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="K202" s="244"/>
       <c r="L202" s="267" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M202" s="244"/>
       <c r="N202" s="267" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="O202" s="244"/>
       <c r="P202" s="290" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q202" s="302"/>
     </row>
@@ -9839,10 +9832,10 @@
       <c r="N203" s="228"/>
       <c r="O203" s="270"/>
       <c r="P203" s="292" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q203" s="303" t="s">
         <v>92</v>
-      </c>
-      <c r="Q203" s="303" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="204" ht="18.75" spans="1:17">
@@ -9856,57 +9849,57 @@
       <c r="H204" s="275"/>
       <c r="I204" s="293"/>
       <c r="J204" s="294" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K204" s="274"/>
       <c r="L204" s="294" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M204" s="274"/>
       <c r="N204" s="294" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O204" s="274"/>
       <c r="P204" s="295" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q204" s="304" t="s">
         <v>97</v>
-      </c>
-      <c r="Q204" s="304" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="205" ht="18" spans="1:17">
       <c r="A205" s="276" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B205" s="277"/>
       <c r="C205" s="278"/>
       <c r="D205" s="277" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E205" s="277"/>
       <c r="F205" s="278"/>
       <c r="G205" s="277" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H205" s="277"/>
       <c r="I205" s="278"/>
       <c r="J205" s="277" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K205" s="278"/>
       <c r="L205" s="277" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M205" s="278"/>
       <c r="N205" s="277" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="O205" s="278"/>
       <c r="P205" s="278" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Q205" s="305" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="206" spans="1:17">
